--- a/datasets/20261021_recontrataciones_san luis potosi.xlsx
+++ b/datasets/20261021_recontrataciones_san luis potosi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luz.ortiz\Desktop\CAPA 2026\PEF\Contratación\261021 Avance de contratación\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INE\Documents\reductor_dias\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C2C9199-DAAD-4B1E-BC7B-499B854FFA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795A8D6-66DF-4768-96F3-9266EC183411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance" sheetId="8" r:id="rId1"/>
@@ -504,78 +504,78 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,69 +981,69 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:AY54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.7265625" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="19" width="14.5703125" customWidth="1"/>
-    <col min="20" max="20" width="18.5703125" customWidth="1"/>
-    <col min="21" max="21" width="22.7109375" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="7" max="19" width="14.54296875" customWidth="1"/>
+    <col min="20" max="20" width="18.54296875" customWidth="1"/>
+    <col min="21" max="21" width="22.7265625" customWidth="1"/>
+    <col min="22" max="22" width="2.7265625" customWidth="1"/>
     <col min="23" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="16384" width="11.42578125" hidden="1"/>
+    <col min="52" max="16384" width="11.453125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="C2" s="28" t="s">
+    <row r="2" spans="2:22" s="2" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+      <c r="C2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-    </row>
-    <row r="3" spans="2:22" s="2" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C3" s="29" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+    </row>
+    <row r="3" spans="2:22" s="2" customFormat="1" ht="20" x14ac:dyDescent="0.3">
+      <c r="C3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-    </row>
-    <row r="4" spans="2:22" s="2" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+    </row>
+    <row r="4" spans="2:22" s="2" customFormat="1" ht="20" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -1064,93 +1064,93 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="2:22" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="C5" s="14" t="s">
+    <row r="5" spans="2:22" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.5">
+      <c r="C5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
     </row>
-    <row r="6" spans="2:22" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="C6" s="15" t="s">
+    <row r="6" spans="2:22" s="2" customFormat="1" ht="25" x14ac:dyDescent="0.5">
+      <c r="C6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
       <c r="T6" s="6"/>
       <c r="U6" s="6"/>
     </row>
-    <row r="7" spans="2:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
+    <row r="7" spans="2:22" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="2:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="17" t="s">
+    <row r="8" spans="2:22" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="B8" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18">
+      <c r="C8" s="27"/>
+      <c r="D8" s="33">
         <v>46316</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="35"/>
     </row>
     <row r="9" spans="2:22" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
     </row>
     <row r="10" spans="2:22" s="2" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
@@ -1159,30 +1159,30 @@
       <c r="C10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="34" t="s">
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="35"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="29"/>
       <c r="T10" s="16" t="s">
         <v>17</v>
       </c>
@@ -1193,20 +1193,20 @@
     <row r="11" spans="2:22" s="2" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="21" t="s">
+      <c r="D11" s="30"/>
+      <c r="E11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="23" t="s">
         <v>16</v>
       </c>
       <c r="J11" s="25" t="s">
@@ -1224,19 +1224,19 @@
       <c r="N11" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="21" t="s">
+      <c r="O11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="21" t="s">
+      <c r="P11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="Q11" s="21" t="s">
+      <c r="Q11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="R11" s="21" t="s">
+      <c r="R11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="S11" s="23" t="s">
+      <c r="S11" s="36" t="s">
         <v>16</v>
       </c>
       <c r="T11" s="16"/>
@@ -1249,28 +1249,28 @@
       <c r="C12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
       <c r="J12" s="26"/>
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
       <c r="N12" s="26"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="37"/>
       <c r="T12" s="16"/>
       <c r="U12" s="16"/>
     </row>
-    <row r="13" spans="2:22" s="37" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>32</v>
@@ -1328,9 +1328,9 @@
         <v>162</v>
       </c>
       <c r="U13" s="12"/>
-      <c r="V13" s="38"/>
-    </row>
-    <row r="14" spans="2:22" s="37" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V13" s="15"/>
+    </row>
+    <row r="14" spans="2:22" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>20</v>
       </c>
@@ -1389,9 +1389,9 @@
         <v>92</v>
       </c>
       <c r="U14" s="12"/>
-      <c r="V14" s="38"/>
-    </row>
-    <row r="15" spans="2:22" s="37" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V14" s="15"/>
+    </row>
+    <row r="15" spans="2:22" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1451,9 +1451,9 @@
         <v>129</v>
       </c>
       <c r="U15" s="12"/>
-      <c r="V15" s="38"/>
-    </row>
-    <row r="16" spans="2:22" s="37" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="V15" s="15"/>
+    </row>
+    <row r="16" spans="2:22" s="14" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="U16" s="12"/>
     </row>
-    <row r="17" spans="2:21" s="37" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:21" s="14" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="U17" s="12"/>
     </row>
-    <row r="18" spans="2:21" s="37" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:21" s="14" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="U18" s="12"/>
     </row>
-    <row r="19" spans="2:21" s="37" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:21" s="14" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>20</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="U19" s="12"/>
     </row>
-    <row r="20" spans="2:21" s="37" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:21" s="14" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="10"/>
@@ -1715,7 +1715,7 @@
       <c r="T20" s="12"/>
       <c r="U20" s="12"/>
     </row>
-    <row r="21" spans="2:21" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:21" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="10"/>
@@ -1737,7 +1737,7 @@
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
     </row>
-    <row r="22" spans="2:21" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:21" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="10"/>
@@ -1759,7 +1759,7 @@
       <c r="T22" s="12"/>
       <c r="U22" s="12"/>
     </row>
-    <row r="23" spans="2:21" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:21" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="10"/>
@@ -1781,7 +1781,7 @@
       <c r="T23" s="12"/>
       <c r="U23" s="12"/>
     </row>
-    <row r="24" spans="2:21" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:21" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="10"/>
@@ -1803,7 +1803,7 @@
       <c r="T24" s="12"/>
       <c r="U24" s="12"/>
     </row>
-    <row r="25" spans="2:21" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:21" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="10"/>
@@ -1825,7 +1825,7 @@
       <c r="T25" s="12"/>
       <c r="U25" s="12"/>
     </row>
-    <row r="26" spans="2:21" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:21" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="10"/>
@@ -1847,7 +1847,7 @@
       <c r="T26" s="12"/>
       <c r="U26" s="12"/>
     </row>
-    <row r="27" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="10"/>
@@ -1869,7 +1869,7 @@
       <c r="T27" s="12"/>
       <c r="U27" s="12"/>
     </row>
-    <row r="28" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="10"/>
@@ -1891,7 +1891,7 @@
       <c r="T28" s="12"/>
       <c r="U28" s="12"/>
     </row>
-    <row r="29" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="10"/>
@@ -1913,7 +1913,7 @@
       <c r="T29" s="12"/>
       <c r="U29" s="12"/>
     </row>
-    <row r="30" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="10"/>
@@ -1935,7 +1935,7 @@
       <c r="T30" s="12"/>
       <c r="U30" s="12"/>
     </row>
-    <row r="31" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="10"/>
@@ -1957,7 +1957,7 @@
       <c r="T31" s="12"/>
       <c r="U31" s="12"/>
     </row>
-    <row r="32" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="10"/>
@@ -1979,7 +1979,7 @@
       <c r="T32" s="12"/>
       <c r="U32" s="12"/>
     </row>
-    <row r="33" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="10"/>
@@ -2001,7 +2001,7 @@
       <c r="T33" s="12"/>
       <c r="U33" s="12"/>
     </row>
-    <row r="34" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="10"/>
@@ -2023,7 +2023,7 @@
       <c r="T34" s="12"/>
       <c r="U34" s="12"/>
     </row>
-    <row r="35" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="10"/>
@@ -2045,7 +2045,7 @@
       <c r="T35" s="12"/>
       <c r="U35" s="12"/>
     </row>
-    <row r="36" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="10"/>
@@ -2067,7 +2067,7 @@
       <c r="T36" s="12"/>
       <c r="U36" s="12"/>
     </row>
-    <row r="37" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="10"/>
@@ -2089,7 +2089,7 @@
       <c r="T37" s="12"/>
       <c r="U37" s="12"/>
     </row>
-    <row r="38" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="10"/>
@@ -2111,7 +2111,7 @@
       <c r="T38" s="12"/>
       <c r="U38" s="12"/>
     </row>
-    <row r="39" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="10"/>
@@ -2133,7 +2133,7 @@
       <c r="T39" s="12"/>
       <c r="U39" s="12"/>
     </row>
-    <row r="40" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="10"/>
@@ -2155,7 +2155,7 @@
       <c r="T40" s="12"/>
       <c r="U40" s="12"/>
     </row>
-    <row r="41" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="10"/>
@@ -2177,7 +2177,7 @@
       <c r="T41" s="12"/>
       <c r="U41" s="12"/>
     </row>
-    <row r="42" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="10"/>
@@ -2199,7 +2199,7 @@
       <c r="T42" s="12"/>
       <c r="U42" s="12"/>
     </row>
-    <row r="43" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="10"/>
@@ -2221,7 +2221,7 @@
       <c r="T43" s="12"/>
       <c r="U43" s="12"/>
     </row>
-    <row r="44" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="10"/>
@@ -2243,7 +2243,7 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
     </row>
-    <row r="45" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="10"/>
@@ -2265,7 +2265,7 @@
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
     </row>
-    <row r="46" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="10"/>
@@ -2287,7 +2287,7 @@
       <c r="T46" s="12"/>
       <c r="U46" s="12"/>
     </row>
-    <row r="47" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="10"/>
@@ -2309,7 +2309,7 @@
       <c r="T47" s="12"/>
       <c r="U47" s="12"/>
     </row>
-    <row r="48" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="10"/>
@@ -2331,7 +2331,7 @@
       <c r="T48" s="12"/>
       <c r="U48" s="12"/>
     </row>
-    <row r="49" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="10"/>
@@ -2353,7 +2353,7 @@
       <c r="T49" s="12"/>
       <c r="U49" s="12"/>
     </row>
-    <row r="50" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="10"/>
@@ -2375,7 +2375,7 @@
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
     </row>
-    <row r="51" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="10"/>
@@ -2397,7 +2397,7 @@
       <c r="T51" s="12"/>
       <c r="U51" s="12"/>
     </row>
-    <row r="52" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="10"/>
@@ -2419,7 +2419,7 @@
       <c r="T52" s="12"/>
       <c r="U52" s="12"/>
     </row>
-    <row r="53" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="10"/>
@@ -2441,7 +2441,7 @@
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
     </row>
-    <row r="54" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="10"/>
@@ -2465,6 +2465,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="B9:U9"/>
+    <mergeCell ref="T10:T12"/>
     <mergeCell ref="U10:U12"/>
     <mergeCell ref="C2:U2"/>
     <mergeCell ref="C3:U3"/>
@@ -2481,21 +2496,6 @@
     <mergeCell ref="Q11:Q12"/>
     <mergeCell ref="R11:R12"/>
     <mergeCell ref="C5:S5"/>
-    <mergeCell ref="C6:S6"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="B9:U9"/>
-    <mergeCell ref="T10:T12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
